--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:00:52+00:00</t>
+    <t>2026-05-04T08:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5495" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4547" uniqueCount="638">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:15:17+00:00</t>
+    <t>2026-06-15T08:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1692,6 +1692,9 @@
     <t>element:Goal</t>
   </si>
   <si>
+    <t>element:EpisodeOfCare</t>
+  </si>
+  <si>
     <t>Extension.id</t>
   </si>
   <si>
@@ -1737,11 +1740,270 @@
     <t>Onkologische Therapielinie</t>
   </si>
   <si>
-    <t>Eine onkologische Therapielinie (Line of Therapy, LoT) auf Basis von `CarePlan`, EnLiST-konform. Eine Therapielinie ist ein Behandlungsabschnitt mit einer bestimmten Intention, die durch ein definiertes Ereignis (Progress, Toxizität, Patientenwunsch, Studienende, geplanter Wechsel) beendet wird. Trägt die Therapieintention der Linie (`onko-therapy-intent`) und gehört über `partOf` zu einem übergeordneten `OnkoCarePlan`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/onko-care-plan)
+    <t>Eine onkologische Therapielinie (Line of Therapy, LoT) auf Basis von `EpisodeOfCare`, EnLiST-konform. Eine Therapielinie ist ein Behandlungsabschnitt mit einer bestimmten Intention und einer definierten Tumorerkrankung, der durch ein klinisches Ereignis (Progress, Toxizität, Patientenwunsch, Studienende, geplanter Wechsel) beendet wird. Die Verbindung zu einem `OnkoCarePlan` erfolgt über `CarePlan.encounter` → `Encounter.episodeOfCare` oder die Standard-Extension `workflow-episodeOfCare`.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/EpisodeOfCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case Program Problem
 </t>
+  </si>
+  <si>
+    <t>An association of a Patient with an Organization and  Healthcare Provider(s) for a period of time that the Organization assumes some level of responsibility</t>
+  </si>
+  <si>
+    <t>An association between a patient and an organization / healthcare provider(s) during which time encounters may occur. The managing organization assumes a level of responsibility for the patient during this time.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.id</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.meta</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.implicitRules</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.language</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.text</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.contained</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.extension</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.extension:therapyIntent</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.modifierExtension</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.identifier</t>
+  </si>
+  <si>
+    <t>Business Identifier(s) relevant for this EpisodeOfCare</t>
+  </si>
+  <si>
+    <t>The EpisodeOfCare may be known by different identifiers for different contexts of use, such as when an external agency is tracking the Episode for funding purposes.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.status</t>
+  </si>
+  <si>
+    <t>planned | waitlist | active | onhold | finished | cancelled | entered-in-error</t>
+  </si>
+  <si>
+    <t>planned | waitlist | active | onhold | finished | cancelled.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the episode as not currently valid.</t>
+  </si>
+  <si>
+    <t>The status of the episode of care.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/episode-of-care-status|4.0.1</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.statusHistory</t>
+  </si>
+  <si>
+    <t>Past list of status codes (the current status may be included to cover the start date of the status)</t>
+  </si>
+  <si>
+    <t>The history of statuses that the EpisodeOfCare has been through (without requiring processing the history of the resource).</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.statusHistory.id</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.statusHistory.extension</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.statusHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.statusHistory.status</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.statusHistory.period</t>
+  </si>
+  <si>
+    <t>Duration the EpisodeOfCare was in the specified status</t>
+  </si>
+  <si>
+    <t>The period during this EpisodeOfCare that the specific status applied.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.type</t>
+  </si>
+  <si>
+    <t>Type/class  - e.g. specialist referral, disease management</t>
+  </si>
+  <si>
+    <t>A classification of the type of episode of care; e.g. specialist referral, disease management, type of funded care.</t>
+  </si>
+  <si>
+    <t>The type can be very important in processing as this could be used in determining if the EpisodeOfCare is relevant to specific government reporting, or other types of classifications.</t>
+  </si>
+  <si>
+    <t>The type of the episode of care.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/episodeofcare-type|4.0.1</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.diagnosis</t>
+  </si>
+  <si>
+    <t>The list of diagnosis relevant to this episode of care</t>
+  </si>
+  <si>
+    <t>The list of diagnosis relevant to this episode of care.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.diagnosis.id</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.diagnosis.extension</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.diagnosis.modifierExtension</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.diagnosis.condition</t>
+  </si>
+  <si>
+    <t>Conditions/problems/diagnoses this episode of care is for</t>
+  </si>
+  <si>
+    <t>A list of conditions/problems/diagnoses that this episode of care is intended to be providing care for.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.diagnosis.role</t>
+  </si>
+  <si>
+    <t>Role that this diagnosis has within the episode of care (e.g. admission, billing, discharge …)</t>
+  </si>
+  <si>
+    <t>Role that this diagnosis has within the episode of care (e.g. admission, billing, discharge …).</t>
+  </si>
+  <si>
+    <t>The type of diagnosis this condition represents.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.diagnosis.rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>Ranking of the diagnosis (for each role type)</t>
+  </si>
+  <si>
+    <t>Ranking of the diagnosis (for each role type).</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The patient who is the focus of this episode of care</t>
+  </si>
+  <si>
+    <t>The patient who is the focus of this episode of care.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.managingOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that assumes care</t>
+  </si>
+  <si>
+    <t>The organization that has assumed the specific responsibilities for the specified duration.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.period</t>
+  </si>
+  <si>
+    <t>Interval during responsibility is assumed</t>
+  </si>
+  <si>
+    <t>The interval during which the managing organization assumes the defined responsibility.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.referralRequest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Originating Referral Request(s)</t>
+  </si>
+  <si>
+    <t>Referral Request(s) that are fulfilled by this EpisodeOfCare, incoming referrals.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.careManager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Care manager/care coordinator for the patient</t>
+  </si>
+  <si>
+    <t>The practitioner that is the care manager/care coordinator for this patient.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CareTeam
+</t>
+  </si>
+  <si>
+    <t>Other practitioners facilitating this episode of care</t>
+  </si>
+  <si>
+    <t>The list of practitioners that may be facilitating this episode of care for specific purposes.</t>
+  </si>
+  <si>
+    <t>EpisodeOfCare.account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Account|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The set of accounts that may be used for billing for this EpisodeOfCare</t>
+  </si>
+  <si>
+    <t>The set of accounts that may be used for billing for this EpisodeOfCare.</t>
+  </si>
+  <si>
+    <t>The billing system may choose to allocate billable items associated with the EpisodeOfCare to different referenced Accounts based on internal business rules.</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B86"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2385,24 +2647,24 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="1">
+      <c r="A66" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B66" t="s" s="1">
+      <c r="B67" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>547</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>548</v>
@@ -2410,23 +2672,23 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>7</v>
+        <v>549</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>549</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>550</v>
@@ -2434,115 +2696,123 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>13</v>
+        <v>551</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B73" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>551</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B79" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>552</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>34</v>
+        <v>553</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>36</v>
+        <v>554</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B86" t="s" s="2">
+      <c r="B87" t="s" s="2">
         <v>38</v>
       </c>
     </row>
@@ -2553,12 +2823,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK160"/>
+  <dimension ref="A1:AK132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.60546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.58203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="2" max="2" width="38.19921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="38.19921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="11.66796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -12603,10 +12873,10 @@
         <v>528</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12706,10 +12976,10 @@
         <v>528</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12780,7 +13050,7 @@
         <v>130</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AE97" t="s" s="2">
         <v>78</v>
@@ -12809,10 +13079,10 @@
         <v>528</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12838,13 +13108,13 @@
         <v>98</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
@@ -12894,7 +13164,7 @@
         <v>78</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>84</v>
@@ -12914,10 +13184,10 @@
         <v>528</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12943,10 +13213,10 @@
         <v>193</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -12977,7 +13247,7 @@
       </c>
       <c r="Z99" s="2"/>
       <c r="AA99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AB99" t="s" s="2">
         <v>78</v>
@@ -12995,7 +13265,7 @@
         <v>78</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
@@ -13012,17 +13282,17 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>32</v>
+        <v>553</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>32</v>
+        <v>553</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
-        <v>75</v>
+        <v>555</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s" s="2">
@@ -13044,10 +13314,10 @@
         <v>79</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>80</v>
+        <v>556</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>81</v>
+        <v>557</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -13098,7 +13368,7 @@
         <v>78</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>32</v>
+        <v>553</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -13115,13 +13385,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>83</v>
+        <v>558</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>83</v>
+        <v>558</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13220,13 +13490,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>91</v>
+        <v>559</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>91</v>
+        <v>559</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13323,13 +13593,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>97</v>
+        <v>560</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>97</v>
+        <v>560</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13428,13 +13698,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>103</v>
+        <v>561</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>103</v>
+        <v>561</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13533,13 +13803,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>112</v>
+        <v>562</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>112</v>
+        <v>562</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13638,13 +13908,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>119</v>
+        <v>563</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>119</v>
+        <v>563</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13743,13 +14013,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>126</v>
+        <v>564</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>126</v>
+        <v>564</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13844,13 +14114,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>134</v>
+        <v>565</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>126</v>
+        <v>564</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>135</v>
@@ -13949,13 +14219,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>140</v>
+        <v>566</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>140</v>
+        <v>566</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14056,13 +14326,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>147</v>
+        <v>567</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>147</v>
+        <v>567</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14082,23 +14352,19 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>148</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>149</v>
+        <v>568</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
         <v>78</v>
       </c>
@@ -14146,7 +14412,7 @@
         <v>78</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>147</v>
+        <v>567</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
@@ -14163,13 +14429,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>153</v>
+        <v>570</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>153</v>
+        <v>570</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14177,30 +14443,32 @@
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>155</v>
+        <v>571</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
         <v>78</v>
@@ -14225,13 +14493,13 @@
         <v>78</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="AA111" t="s" s="2">
-        <v>78</v>
+        <v>575</v>
       </c>
       <c r="AB111" t="s" s="2">
         <v>78</v>
@@ -14249,13 +14517,13 @@
         <v>78</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>153</v>
+        <v>570</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>78</v>
@@ -14266,13 +14534,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>157</v>
+        <v>576</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>157</v>
+        <v>576</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14292,20 +14560,18 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>98</v>
+        <v>264</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>158</v>
+        <v>577</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" s="2"/>
       <c r="Q112" t="s" s="2">
         <v>78</v>
@@ -14354,7 +14620,7 @@
         <v>78</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>157</v>
+        <v>576</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -14371,24 +14637,24 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>161</v>
+        <v>579</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>161</v>
+        <v>579</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>78</v>
@@ -14397,21 +14663,19 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="P113" s="2"/>
       <c r="Q113" t="s" s="2">
         <v>78</v>
       </c>
@@ -14459,34 +14723,34 @@
         <v>78</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>161</v>
+        <v>272</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>167</v>
+        <v>580</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>167</v>
+        <v>580</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" t="s" s="2">
@@ -14502,23 +14766,21 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>169</v>
+        <v>274</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>170</v>
+        <v>275</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="P114" s="2"/>
       <c r="Q114" t="s" s="2">
         <v>78</v>
       </c>
@@ -14566,7 +14828,7 @@
         <v>78</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>167</v>
+        <v>276</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>76</v>
@@ -14578,22 +14840,22 @@
         <v>78</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>173</v>
+        <v>581</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>173</v>
+        <v>581</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
-        <v>78</v>
+        <v>278</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" t="s" s="2">
@@ -14603,27 +14865,29 @@
         <v>77</v>
       </c>
       <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>552</v>
+        <v>127</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>174</v>
+        <v>279</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="P115" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="Q115" t="s" s="2">
         <v>78</v>
       </c>
@@ -14671,7 +14935,7 @@
         <v>78</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>173</v>
+        <v>281</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>76</v>
@@ -14683,18 +14947,18 @@
         <v>78</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>177</v>
+        <v>582</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>177</v>
+        <v>582</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -14708,29 +14972,25 @@
         <v>84</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>104</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>178</v>
+        <v>571</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" s="2"/>
       <c r="Q116" t="s" s="2">
         <v>78</v>
       </c>
@@ -14757,10 +15017,10 @@
         <v>182</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>179</v>
+        <v>574</v>
       </c>
       <c r="AA116" t="s" s="2">
-        <v>183</v>
+        <v>575</v>
       </c>
       <c r="AB116" t="s" s="2">
         <v>78</v>
@@ -14778,7 +15038,7 @@
         <v>78</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>177</v>
+        <v>582</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>84</v>
@@ -14795,13 +15055,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>184</v>
+        <v>583</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>184</v>
+        <v>583</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -14815,29 +15075,25 @@
         <v>84</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>185</v>
+        <v>584</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" s="2"/>
       <c r="Q117" t="s" s="2">
         <v>78</v>
       </c>
@@ -14861,13 +15117,13 @@
         <v>78</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AA117" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AB117" t="s" s="2">
         <v>78</v>
@@ -14885,7 +15141,7 @@
         <v>78</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>184</v>
+        <v>583</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>84</v>
@@ -14902,13 +15158,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>192</v>
+        <v>586</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>192</v>
+        <v>586</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -14934,17 +15190,15 @@
         <v>193</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>194</v>
+        <v>587</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>195</v>
+        <v>588</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
         <v>78</v>
       </c>
@@ -14971,10 +15225,10 @@
         <v>198</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>199</v>
+        <v>590</v>
       </c>
       <c r="AA118" t="s" s="2">
-        <v>200</v>
+        <v>591</v>
       </c>
       <c r="AB118" t="s" s="2">
         <v>78</v>
@@ -14992,7 +15246,7 @@
         <v>78</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>192</v>
+        <v>586</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>76</v>
@@ -15009,13 +15263,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>201</v>
+        <v>592</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>201</v>
+        <v>592</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -15023,13 +15277,13 @@
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J119" t="s" s="2">
         <v>78</v>
@@ -15038,13 +15292,13 @@
         <v>85</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>203</v>
+        <v>593</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>204</v>
+        <v>594</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
@@ -15095,13 +15349,13 @@
         <v>78</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>201</v>
+        <v>592</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>78</v>
@@ -15112,13 +15366,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>205</v>
+        <v>595</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>205</v>
+        <v>595</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -15138,21 +15392,19 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>202</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="P120" s="2"/>
       <c r="Q120" t="s" s="2">
         <v>78</v>
       </c>
@@ -15200,7 +15452,7 @@
         <v>78</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>205</v>
+        <v>272</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>76</v>
@@ -15212,49 +15464,51 @@
         <v>78</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>209</v>
+        <v>596</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>209</v>
+        <v>596</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>212</v>
+        <v>274</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P121" s="2"/>
       <c r="Q121" t="s" s="2">
         <v>78</v>
@@ -15303,64 +15557,66 @@
         <v>78</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>214</v>
+        <v>597</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>214</v>
+        <v>597</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
-        <v>78</v>
+        <v>278</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>215</v>
+        <v>127</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>216</v>
+        <v>279</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="P122" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="Q122" t="s" s="2">
         <v>78</v>
       </c>
@@ -15408,34 +15664,34 @@
         <v>78</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>219</v>
+        <v>598</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>219</v>
+        <v>598</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" t="s" s="2">
@@ -15454,20 +15710,16 @@
         <v>85</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>222</v>
+        <v>599</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" s="2"/>
       <c r="Q123" t="s" s="2">
         <v>78</v>
       </c>
@@ -15515,10 +15767,10 @@
         <v>78</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>219</v>
+        <v>598</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>84</v>
@@ -15532,17 +15784,17 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>226</v>
+        <v>601</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>226</v>
+        <v>601</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" t="s" s="2">
@@ -15552,7 +15804,7 @@
         <v>84</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>78</v>
@@ -15561,13 +15813,13 @@
         <v>85</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>229</v>
+        <v>602</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>230</v>
+        <v>603</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -15594,13 +15846,13 @@
         <v>78</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>78</v>
+        <v>604</v>
       </c>
       <c r="AA124" t="s" s="2">
-        <v>78</v>
+        <v>605</v>
       </c>
       <c r="AB124" t="s" s="2">
         <v>78</v>
@@ -15618,7 +15870,7 @@
         <v>78</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>226</v>
+        <v>601</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -15635,13 +15887,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>231</v>
+        <v>606</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>231</v>
+        <v>606</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -15655,7 +15907,7 @@
         <v>84</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J125" t="s" s="2">
         <v>78</v>
@@ -15664,17 +15916,15 @@
         <v>85</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>232</v>
+        <v>607</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>233</v>
+        <v>608</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" s="2"/>
       <c r="Q125" t="s" s="2">
         <v>78</v>
@@ -15723,7 +15973,7 @@
         <v>78</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>231</v>
+        <v>606</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>76</v>
@@ -15740,13 +15990,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>236</v>
+        <v>610</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>236</v>
+        <v>610</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -15754,32 +16004,30 @@
       </c>
       <c r="F126" s="2"/>
       <c r="G126" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>232</v>
+        <v>611</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>237</v>
+        <v>612</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="O126" s="2"/>
       <c r="P126" s="2"/>
       <c r="Q126" t="s" s="2">
         <v>78</v>
@@ -15828,13 +16076,13 @@
         <v>78</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>236</v>
+        <v>610</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>78</v>
@@ -15845,13 +16093,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>240</v>
+        <v>614</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>240</v>
+        <v>614</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -15862,30 +16110,28 @@
         <v>76</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>241</v>
+        <v>615</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>242</v>
+        <v>616</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>243</v>
+        <v>617</v>
       </c>
       <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="P127" s="2"/>
       <c r="Q127" t="s" s="2">
         <v>78</v>
       </c>
@@ -15933,13 +16179,13 @@
         <v>78</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>240</v>
+        <v>614</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>78</v>
@@ -15950,13 +16196,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>245</v>
+        <v>618</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>245</v>
+        <v>618</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -15967,7 +16213,7 @@
         <v>84</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>85</v>
@@ -15979,20 +16225,16 @@
         <v>85</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>247</v>
+        <v>619</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" s="2"/>
       <c r="Q128" t="s" s="2">
         <v>78</v>
       </c>
@@ -16040,13 +16282,13 @@
         <v>78</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>245</v>
+        <v>618</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>78</v>
@@ -16057,13 +16299,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>251</v>
+        <v>621</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>251</v>
+        <v>621</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -16086,20 +16328,16 @@
         <v>78</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>252</v>
+        <v>622</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>253</v>
+        <v>623</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" s="2"/>
       <c r="Q129" t="s" s="2">
         <v>78</v>
       </c>
@@ -16147,7 +16385,7 @@
         <v>78</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>251</v>
+        <v>621</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>76</v>
@@ -16164,13 +16402,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>257</v>
+        <v>625</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>257</v>
+        <v>625</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16181,7 +16419,7 @@
         <v>76</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>85</v>
@@ -16193,20 +16431,16 @@
         <v>78</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>258</v>
+        <v>626</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>259</v>
+        <v>627</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="O130" s="2"/>
+      <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
         <v>78</v>
       </c>
@@ -16254,13 +16488,13 @@
         <v>78</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>257</v>
+        <v>625</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>78</v>
@@ -16271,17 +16505,17 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>263</v>
+        <v>629</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>263</v>
+        <v>629</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
-        <v>78</v>
+        <v>630</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" t="s" s="2">
@@ -16300,18 +16534,16 @@
         <v>78</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>265</v>
+        <v>631</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>266</v>
+        <v>632</v>
       </c>
       <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
         <v>78</v>
       </c>
@@ -16359,7 +16591,7 @@
         <v>78</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>263</v>
+        <v>629</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -16371,18 +16603,18 @@
         <v>78</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>268</v>
+        <v>96</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>269</v>
+        <v>633</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>269</v>
+        <v>633</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16393,7 +16625,7 @@
         <v>76</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>78</v>
@@ -16405,15 +16637,17 @@
         <v>78</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>202</v>
+        <v>634</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>270</v>
+        <v>635</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
         <v>78</v>
@@ -16462,2974 +16696,18 @@
         <v>78</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>272</v>
+        <v>633</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C133" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="D133" s="2"/>
-      <c r="E133" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="F133" s="2"/>
-      <c r="G133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P133" s="2"/>
-      <c r="Q133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R133" s="2"/>
-      <c r="S133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="D134" s="2"/>
-      <c r="E134" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="F134" s="2"/>
-      <c r="G134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P134" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Q134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R134" s="2"/>
-      <c r="S134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="D135" s="2"/>
-      <c r="E135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F135" s="2"/>
-      <c r="G135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="P135" s="2"/>
-      <c r="Q135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R135" s="2"/>
-      <c r="S135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="D136" s="2"/>
-      <c r="E136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F136" s="2"/>
-      <c r="G136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="P136" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Q136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R136" s="2"/>
-      <c r="S136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="D137" s="2"/>
-      <c r="E137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F137" s="2"/>
-      <c r="G137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="P137" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Q137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R137" s="2"/>
-      <c r="S137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="D138" s="2"/>
-      <c r="E138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F138" s="2"/>
-      <c r="G138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="P138" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="Q138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R138" s="2"/>
-      <c r="S138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="D139" s="2"/>
-      <c r="E139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F139" s="2"/>
-      <c r="G139" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="Q139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R139" s="2"/>
-      <c r="S139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="D140" s="2"/>
-      <c r="E140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F140" s="2"/>
-      <c r="G140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O140" s="2"/>
-      <c r="P140" s="2"/>
-      <c r="Q140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R140" s="2"/>
-      <c r="S140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="D141" s="2"/>
-      <c r="E141" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="F141" s="2"/>
-      <c r="G141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P141" s="2"/>
-      <c r="Q141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R141" s="2"/>
-      <c r="S141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C142" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="D142" s="2"/>
-      <c r="E142" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="F142" s="2"/>
-      <c r="G142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P142" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Q142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R142" s="2"/>
-      <c r="S142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="D143" s="2"/>
-      <c r="E143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F143" s="2"/>
-      <c r="G143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="Q143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R143" s="2"/>
-      <c r="S143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="D144" s="2"/>
-      <c r="E144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F144" s="2"/>
-      <c r="G144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O144" s="2"/>
-      <c r="P144" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Q144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R144" s="2"/>
-      <c r="S144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="D145" s="2"/>
-      <c r="E145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F145" s="2"/>
-      <c r="G145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="P145" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Q145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R145" s="2"/>
-      <c r="S145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="D146" s="2"/>
-      <c r="E146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F146" s="2"/>
-      <c r="G146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="P146" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="Q146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R146" s="2"/>
-      <c r="S146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="D147" s="2"/>
-      <c r="E147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F147" s="2"/>
-      <c r="G147" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="P147" s="2"/>
-      <c r="Q147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R147" s="2"/>
-      <c r="S147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK147" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C148" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="D148" s="2"/>
-      <c r="E148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F148" s="2"/>
-      <c r="G148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="P148" s="2"/>
-      <c r="Q148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R148" s="2"/>
-      <c r="S148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="D149" s="2"/>
-      <c r="E149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F149" s="2"/>
-      <c r="G149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O149" s="2"/>
-      <c r="P149" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="Q149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R149" s="2"/>
-      <c r="S149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="D150" s="2"/>
-      <c r="E150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F150" s="2"/>
-      <c r="G150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="Q150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R150" s="2"/>
-      <c r="S150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="D151" s="2"/>
-      <c r="E151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F151" s="2"/>
-      <c r="G151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="P151" s="2"/>
-      <c r="Q151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R151" s="2"/>
-      <c r="S151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="D152" s="2"/>
-      <c r="E152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F152" s="2"/>
-      <c r="G152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="Q152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R152" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C153" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="D153" s="2"/>
-      <c r="E153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F153" s="2"/>
-      <c r="G153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="Q153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R153" s="2"/>
-      <c r="S153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="D154" s="2"/>
-      <c r="E154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F154" s="2"/>
-      <c r="G154" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="P154" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="Q154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R154" s="2"/>
-      <c r="S154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="D155" s="2"/>
-      <c r="E155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F155" s="2"/>
-      <c r="G155" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="P155" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="Q155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R155" s="2"/>
-      <c r="S155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C156" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="D156" s="2"/>
-      <c r="E156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F156" s="2"/>
-      <c r="G156" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O156" s="2"/>
-      <c r="P156" s="2"/>
-      <c r="Q156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R156" s="2"/>
-      <c r="S156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C157" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="D157" s="2"/>
-      <c r="E157" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="F157" s="2"/>
-      <c r="G157" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O157" s="2"/>
-      <c r="P157" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="Q157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R157" s="2"/>
-      <c r="S157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="D158" s="2"/>
-      <c r="E158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F158" s="2"/>
-      <c r="G158" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O158" s="2"/>
-      <c r="P158" s="2"/>
-      <c r="Q158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R158" s="2"/>
-      <c r="S158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="D159" s="2"/>
-      <c r="E159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F159" s="2"/>
-      <c r="G159" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O159" s="2"/>
-      <c r="P159" s="2"/>
-      <c r="Q159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R159" s="2"/>
-      <c r="S159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="D160" s="2"/>
-      <c r="E160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F160" s="2"/>
-      <c r="G160" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O160" s="2"/>
-      <c r="P160" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="Q160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R160" s="2"/>
-      <c r="S160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK160" t="s" s="2">
         <v>96</v>
       </c>
     </row>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:40:43+00:00</t>
+    <t>2026-06-15T08:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4547" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4547" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:59:58+00:00</t>
+    <t>2026-06-18T07:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,21 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Onkologischer Versorgungsplan auf Basis von `CarePlan`. Trägt die Therapieintention (Extension `onko-therapy-intent`), referenziert die adressierte Krebserkrankung (`addresses`), die übergeordneten Therapieziele (`goal` → `OnkoTherapyGoal`) sowie die Therapielinien als untergeordnete Pläne (`CarePlan.partOf` von `OnkoTherapyLine`). Im Fallback-Pfad (keine computable Leitlinie) ist der CarePlan die führende Repräsentation des realen Versorgungsverlaufs; im Primärpfad referenziert er via `instantiatesCanonical` eine `PlanDefinition` aus dem CPG-on-FHIR-Stack.</t>
+    <t>Onkologischer Versorgungsplan auf Basis von `CarePlan`.
+Das Profil ist architektonisch an den **HL7 FHIR US Multiple Chronic Conditions (MCC) eCare Plan**
+([MCCCarePlan](https://build.fhir.org/ig/HL7/fhir-us-mcc/StructureDefinition-MCCCarePlan.html))
+angelehnt: Der CarePlan ist das zentrale, konsensbasierte Steuerobjekt, das adressierte
+Erkrankungen (`addresses`), übergeordnete Ziele (`goal`) sowie geplante und durchgeführte
+Maßnahmen (`activity`) verschiedener Versorgungsteams zusammenführt.
+Onkologiespezifische Ergänzungen gegenüber MCC:
+- Therapieintention über die Extension `onko-therapy-intent` (kurativ, neoadjuvant, adjuvant,
+  Erhaltung, palliativ, supportiv).
+- `goal` referenziert das Profil `OnkoTherapyGoal`.
+- Therapielinien (`OnkoTherapyLine`, Basis `EpisodeOfCare`) werden über `CarePlan.encounter`
+  bzw. die Standard-Extension `workflow-episodeOfCare` verknüpft.
+Im Fallback-Pfad (keine computable Leitlinie) ist der CarePlan die führende Repräsentation des
+realen Versorgungsverlaufs; im Primärpfad referenziert er via `instantiatesCanonical` eine
+`PlanDefinition` aus dem CPG-on-FHIR-Stack.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -925,6 +939,10 @@
     <t>CarePlan.activity.outcomeReference</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Procedure|Observation|MedicationAdministration|DiagnosticReport)
+</t>
+  </si>
+  <si>
     <t>Appointment, Encounter, Procedure, etc.</t>
   </si>
   <si>
@@ -959,7 +977,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
+    <t xml:space="preserve">Reference(Appointment|MedicationRequest|NutritionOrder|Task|ServiceRequest|RequestGroup)
 </t>
   </si>
   <si>
@@ -1297,7 +1315,22 @@
     <t>Onkologisches Therapieziel</t>
   </si>
   <si>
-    <t>Strukturiertes onkologisches Therapieziel auf Basis von `Goal`. Die Zielart wird über `category` codiert (Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme). Über die Extension `onko-therapy-intent` kann zusätzlich die Therapieintention der zugehörigen Behandlungslinie hinterlegt werden. Das Ziel referenziert über `addresses` die adressierte Tumorerkrankung und kann über `Goal.outcomeReference` an Verlaufs-Observations (z. B. mCODE CancerDiseaseStatus) gebunden werden.</t>
+    <t>Strukturiertes onkologisches Therapieziel auf Basis von `Goal`.
+Das Profil ist an den **HL7 FHIR US Multiple Chronic Conditions (MCC) eCare Plan**
+([MCCGoal](https://build.fhir.org/ig/HL7/fhir-us-mcc/StructureDefinition-MCCGoal.html))
+angelehnt: Das Therapieziel ist eine eigenständige, referenzbasierte Ressource, die über
+`addresses` mit den adressierten Erkrankungen und über `outcomeReference` mit beobachteten
+Ergebnissen (Verlaufs-Observations) verknüpft wird.
+Onkologiespezifische Ergänzungen gegenüber MCC:
+- Die Zielart wird über `category` aus `OnkoTherapyGoalTypeVS` codiert (Heilung,
+  Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme).
+- Über die Extension `onko-therapy-intent` kann zusätzlich die Therapieintention der
+  zugehörigen Behandlungslinie hinterlegt werden.
+- `outcomeReference` bindet das Ziel an Verlaufs-Observations (z. B. mCODE
+  CancerDiseaseStatus / Response Assessment), wodurch das Tumoransprechen auf das Ziel
+  bezogen ausgewertet werden kann.
+`achievementStatus` bildet — analog MCC — den Erreichungsgrad bzw. die Zielakzeptanz ab
+(z. B. erreicht, in Bearbeitung, nicht erreicht).</t>
   </si>
   <si>
     <t>Goal</t>
@@ -2319,7 +2352,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24">
@@ -2327,7 +2360,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25">
@@ -2343,7 +2376,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27">
@@ -2351,7 +2384,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="28">
@@ -2405,7 +2438,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35">
@@ -2441,7 +2474,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="40">
@@ -2449,7 +2482,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="41">
@@ -2481,7 +2514,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="45">
@@ -2489,7 +2522,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="46">
@@ -2505,7 +2538,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="48">
@@ -2595,7 +2628,7 @@
         <v>29</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="60">
@@ -2611,7 +2644,7 @@
         <v>33</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="62">
@@ -2632,26 +2665,26 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="67">
@@ -2667,7 +2700,7 @@
         <v>2</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69">
@@ -2675,7 +2708,7 @@
         <v>4</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70">
@@ -2691,7 +2724,7 @@
         <v>8</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="72">
@@ -2699,7 +2732,7 @@
         <v>10</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="73">
@@ -2753,7 +2786,7 @@
         <v>23</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="80">
@@ -2789,7 +2822,7 @@
         <v>31</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="85">
@@ -2797,7 +2830,7 @@
         <v>33</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="86">
@@ -3832,7 +3865,7 @@
         <v>84</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
@@ -4888,7 +4921,7 @@
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>78</v>
@@ -5621,7 +5654,7 @@
         <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>78</v>
@@ -5726,7 +5759,7 @@
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>78</v>
@@ -6043,7 +6076,7 @@
         <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>78</v>
@@ -6782,7 +6815,7 @@
         <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>78</v>
@@ -6791,19 +6824,19 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q38" t="s" s="2">
         <v>78</v>
@@ -6872,10 +6905,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6898,19 +6931,19 @@
         <v>78</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q39" t="s" s="2">
         <v>78</v>
@@ -6959,7 +6992,7 @@
         <v>78</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
@@ -6979,10 +7012,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6996,7 +7029,7 @@
         <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>78</v>
@@ -7005,19 +7038,19 @@
         <v>78</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q40" t="s" s="2">
         <v>78</v>
@@ -7066,7 +7099,7 @@
         <v>78</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>76</v>
@@ -7075,7 +7108,7 @@
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>96</v>
@@ -7086,10 +7119,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -7115,14 +7148,14 @@
         <v>264</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q41" t="s" s="2">
         <v>78</v>
@@ -7171,16 +7204,16 @@
         <v>78</v>
       </c>
       <c r="AG41" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>96</v>
@@ -7191,10 +7224,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -7294,10 +7327,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -7399,10 +7432,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -7506,10 +7539,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7535,14 +7568,14 @@
         <v>104</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>78</v>
@@ -7570,10 +7603,10 @@
         <v>182</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AB45" t="s" s="2">
         <v>78</v>
@@ -7591,7 +7624,7 @@
         <v>78</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -7611,10 +7644,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7637,17 +7670,17 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>155</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>78</v>
@@ -7696,7 +7729,7 @@
         <v>78</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -7716,10 +7749,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7748,13 +7781,13 @@
         <v>158</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>160</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>78</v>
@@ -7803,7 +7836,7 @@
         <v>78</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -7823,10 +7856,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7852,16 +7885,16 @@
         <v>193</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q48" t="s" s="2">
         <v>78</v>
@@ -7889,10 +7922,10 @@
         <v>198</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AB48" t="s" s="2">
         <v>78</v>
@@ -7910,7 +7943,7 @@
         <v>78</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -7930,10 +7963,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7959,13 +7992,13 @@
         <v>193</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
@@ -7994,10 +8027,10 @@
         <v>198</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AB49" t="s" s="2">
         <v>78</v>
@@ -8015,7 +8048,7 @@
         <v>78</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -8035,10 +8068,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -8061,16 +8094,16 @@
         <v>78</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
@@ -8120,7 +8153,7 @@
         <v>78</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
@@ -8140,10 +8173,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -8166,17 +8199,17 @@
         <v>78</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q51" t="s" s="2">
         <v>78</v>
@@ -8225,7 +8258,7 @@
         <v>78</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -8245,10 +8278,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -8274,16 +8307,16 @@
         <v>104</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q52" t="s" s="2">
         <v>78</v>
@@ -8311,10 +8344,10 @@
         <v>182</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AB52" t="s" s="2">
         <v>78</v>
@@ -8332,7 +8365,7 @@
         <v>78</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>84</v>
@@ -8352,10 +8385,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8381,13 +8414,13 @@
         <v>193</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
@@ -8437,7 +8470,7 @@
         <v>78</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
@@ -8457,10 +8490,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8483,70 +8516,70 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Q54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R54" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG54" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="Q54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
@@ -8566,10 +8599,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8592,17 +8625,17 @@
         <v>78</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>78</v>
@@ -8651,7 +8684,7 @@
         <v>78</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -8671,10 +8704,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8697,19 +8730,19 @@
         <v>78</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P56" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>78</v>
@@ -8758,7 +8791,7 @@
         <v>78</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
@@ -8778,10 +8811,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8804,19 +8837,19 @@
         <v>78</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>78</v>
@@ -8865,7 +8898,7 @@
         <v>78</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
@@ -8885,10 +8918,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8911,13 +8944,13 @@
         <v>78</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -8947,10 +8980,10 @@
         <v>198</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AB58" t="s" s="2">
         <v>78</v>
@@ -8968,7 +9001,7 @@
         <v>78</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
@@ -8988,14 +9021,14 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
@@ -9014,17 +9047,17 @@
         <v>78</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q59" t="s" s="2">
         <v>78</v>
@@ -9073,7 +9106,7 @@
         <v>78</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>76</v>
@@ -9093,10 +9126,10 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -9119,13 +9152,13 @@
         <v>78</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -9176,7 +9209,7 @@
         <v>78</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>76</v>
@@ -9196,10 +9229,10 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -9225,10 +9258,10 @@
         <v>202</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
@@ -9279,7 +9312,7 @@
         <v>78</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>76</v>
@@ -9299,10 +9332,10 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9325,17 +9358,17 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q62" t="s" s="2">
         <v>78</v>
@@ -9384,7 +9417,7 @@
         <v>78</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
@@ -9401,13 +9434,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -9433,10 +9466,10 @@
         <v>79</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>261</v>
@@ -9489,7 +9522,7 @@
         <v>78</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
@@ -9506,13 +9539,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9611,13 +9644,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9714,13 +9747,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9819,13 +9852,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9924,13 +9957,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -10029,13 +10062,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -10134,13 +10167,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10235,13 +10268,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B71" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>135</v>
@@ -10257,7 +10290,7 @@
         <v>84</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>78</v>
@@ -10340,13 +10373,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10447,13 +10480,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10479,16 +10512,16 @@
         <v>148</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>151</v>
       </c>
       <c r="P73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q73" t="s" s="2">
         <v>78</v>
@@ -10537,7 +10570,7 @@
         <v>78</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>76</v>
@@ -10554,13 +10587,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10586,16 +10619,16 @@
         <v>104</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>78</v>
@@ -10623,10 +10656,10 @@
         <v>182</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AB74" t="s" s="2">
         <v>78</v>
@@ -10644,7 +10677,7 @@
         <v>78</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>84</v>
@@ -10661,13 +10694,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10681,7 +10714,7 @@
         <v>84</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>78</v>
@@ -10693,10 +10726,10 @@
         <v>193</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
@@ -10726,10 +10759,10 @@
         <v>108</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AB75" t="s" s="2">
         <v>78</v>
@@ -10747,7 +10780,7 @@
         <v>78</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -10764,13 +10797,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10796,14 +10829,14 @@
         <v>193</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>78</v>
@@ -10828,11 +10861,11 @@
         <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z76" s="2"/>
       <c r="AA76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AB76" t="s" s="2">
         <v>78</v>
@@ -10850,7 +10883,7 @@
         <v>78</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>76</v>
@@ -10867,13 +10900,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10887,7 +10920,7 @@
         <v>84</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>78</v>
@@ -10899,16 +10932,16 @@
         <v>193</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>78</v>
@@ -10936,10 +10969,10 @@
         <v>108</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AB77" t="s" s="2">
         <v>78</v>
@@ -10957,7 +10990,7 @@
         <v>78</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -10974,13 +11007,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11006,16 +11039,16 @@
         <v>193</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q78" t="s" s="2">
         <v>78</v>
@@ -11043,10 +11076,10 @@
         <v>198</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA78" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AB78" t="s" s="2">
         <v>78</v>
@@ -11064,7 +11097,7 @@
         <v>78</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>84</v>
@@ -11081,13 +11114,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11113,14 +11146,14 @@
         <v>211</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q79" t="s" s="2">
         <v>78</v>
@@ -11169,7 +11202,7 @@
         <v>78</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>84</v>
@@ -11186,13 +11219,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11215,17 +11248,17 @@
         <v>85</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q80" t="s" s="2">
         <v>78</v>
@@ -11253,10 +11286,10 @@
         <v>198</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AA80" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AB80" t="s" s="2">
         <v>78</v>
@@ -11274,7 +11307,7 @@
         <v>78</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -11291,13 +11324,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11323,16 +11356,16 @@
         <v>264</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P81" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>78</v>
@@ -11381,7 +11414,7 @@
         <v>78</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -11390,21 +11423,21 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11501,13 +11534,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11606,13 +11639,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11713,13 +11746,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11733,7 +11766,7 @@
         <v>84</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>78</v>
@@ -11745,10 +11778,10 @@
         <v>193</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -11778,10 +11811,10 @@
         <v>198</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA85" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AB85" t="s" s="2">
         <v>78</v>
@@ -11799,7 +11832,7 @@
         <v>78</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -11808,7 +11841,7 @@
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>96</v>
@@ -11816,13 +11849,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11836,7 +11869,7 @@
         <v>84</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>78</v>
@@ -11845,16 +11878,16 @@
         <v>85</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
@@ -11883,7 +11916,7 @@
         <v>198</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -11904,7 +11937,7 @@
         <v>78</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -11913,7 +11946,7 @@
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>96</v>
@@ -11921,13 +11954,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11941,7 +11974,7 @@
         <v>84</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J87" t="s" s="2">
         <v>78</v>
@@ -11950,17 +11983,17 @@
         <v>85</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>78</v>
@@ -12009,7 +12042,7 @@
         <v>78</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
@@ -12026,13 +12059,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12055,16 +12088,16 @@
         <v>85</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
@@ -12114,7 +12147,7 @@
         <v>78</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>76</v>
@@ -12131,13 +12164,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -12163,13 +12196,13 @@
         <v>202</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -12219,7 +12252,7 @@
         <v>78</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -12236,13 +12269,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -12256,7 +12289,7 @@
         <v>84</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>78</v>
@@ -12265,16 +12298,16 @@
         <v>85</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
@@ -12324,7 +12357,7 @@
         <v>78</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>76</v>
@@ -12341,13 +12374,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12370,17 +12403,17 @@
         <v>78</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Q91" t="s" s="2">
         <v>78</v>
@@ -12429,7 +12462,7 @@
         <v>78</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>76</v>
@@ -12446,13 +12479,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -12466,7 +12499,7 @@
         <v>77</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>78</v>
@@ -12475,19 +12508,19 @@
         <v>78</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Q92" t="s" s="2">
         <v>78</v>
@@ -12536,7 +12569,7 @@
         <v>78</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -12553,13 +12586,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12585,16 +12618,16 @@
         <v>193</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P93" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q93" t="s" s="2">
         <v>78</v>
@@ -12622,10 +12655,10 @@
         <v>198</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>78</v>
@@ -12643,7 +12676,7 @@
         <v>78</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -12660,13 +12693,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12689,19 +12722,19 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P94" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>78</v>
@@ -12750,7 +12783,7 @@
         <v>78</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
@@ -12767,7 +12800,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>128</v>
@@ -12870,13 +12903,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12973,13 +13006,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13050,7 +13083,7 @@
         <v>130</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AE97" t="s" s="2">
         <v>78</v>
@@ -13076,13 +13109,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13108,13 +13141,13 @@
         <v>98</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
@@ -13122,7 +13155,7 @@
       </c>
       <c r="R98" s="2"/>
       <c r="S98" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>78</v>
@@ -13164,7 +13197,7 @@
         <v>78</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>84</v>
@@ -13181,13 +13214,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13213,10 +13246,10 @@
         <v>193</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -13247,7 +13280,7 @@
       </c>
       <c r="Z99" s="2"/>
       <c r="AA99" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AB99" t="s" s="2">
         <v>78</v>
@@ -13265,7 +13298,7 @@
         <v>78</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
@@ -13282,17 +13315,17 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s" s="2">
@@ -13314,10 +13347,10 @@
         <v>79</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -13368,7 +13401,7 @@
         <v>78</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -13385,13 +13418,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13490,13 +13523,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13593,13 +13626,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13698,13 +13731,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13803,13 +13836,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13908,13 +13941,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14013,13 +14046,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14114,13 +14147,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B108" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>135</v>
@@ -14219,13 +14252,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14326,13 +14359,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14358,10 +14391,10 @@
         <v>148</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
@@ -14412,7 +14445,7 @@
         <v>78</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
@@ -14429,13 +14462,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14461,13 +14494,13 @@
         <v>104</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
@@ -14496,10 +14529,10 @@
         <v>182</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA111" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AB111" t="s" s="2">
         <v>78</v>
@@ -14517,7 +14550,7 @@
         <v>78</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>84</v>
@@ -14534,13 +14567,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14566,10 +14599,10 @@
         <v>264</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
@@ -14620,7 +14653,7 @@
         <v>78</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -14637,13 +14670,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14740,13 +14773,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -14845,13 +14878,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -14952,13 +14985,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -14984,10 +15017,10 @@
         <v>104</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -15017,10 +15050,10 @@
         <v>182</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA116" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AB116" t="s" s="2">
         <v>78</v>
@@ -15038,7 +15071,7 @@
         <v>78</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>84</v>
@@ -15055,13 +15088,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -15087,10 +15120,10 @@
         <v>221</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -15141,7 +15174,7 @@
         <v>78</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>84</v>
@@ -15158,13 +15191,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -15190,13 +15223,13 @@
         <v>193</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
@@ -15225,10 +15258,10 @@
         <v>198</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA118" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AB118" t="s" s="2">
         <v>78</v>
@@ -15246,7 +15279,7 @@
         <v>78</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>76</v>
@@ -15263,13 +15296,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -15295,10 +15328,10 @@
         <v>264</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
@@ -15349,7 +15382,7 @@
         <v>78</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -15366,13 +15399,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -15469,13 +15502,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -15574,13 +15607,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -15681,13 +15714,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15713,10 +15746,10 @@
         <v>246</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -15767,7 +15800,7 @@
         <v>78</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>84</v>
@@ -15784,13 +15817,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -15816,10 +15849,10 @@
         <v>193</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -15849,10 +15882,10 @@
         <v>108</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA124" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AB124" t="s" s="2">
         <v>78</v>
@@ -15870,7 +15903,7 @@
         <v>78</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -15887,13 +15920,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -15916,13 +15949,13 @@
         <v>85</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -15973,7 +16006,7 @@
         <v>78</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>76</v>
@@ -15990,13 +16023,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16019,13 +16052,13 @@
         <v>85</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -16076,7 +16109,7 @@
         <v>78</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>84</v>
@@ -16093,13 +16126,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -16122,13 +16155,13 @@
         <v>85</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -16179,7 +16212,7 @@
         <v>78</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>76</v>
@@ -16196,13 +16229,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -16228,10 +16261,10 @@
         <v>221</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
@@ -16282,7 +16315,7 @@
         <v>78</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>76</v>
@@ -16299,13 +16332,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -16328,13 +16361,13 @@
         <v>78</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
@@ -16385,7 +16418,7 @@
         <v>78</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>76</v>
@@ -16402,13 +16435,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16431,13 +16464,13 @@
         <v>78</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
@@ -16488,7 +16521,7 @@
         <v>78</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>76</v>
@@ -16505,17 +16538,17 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" t="s" s="2">
@@ -16537,10 +16570,10 @@
         <v>241</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -16591,7 +16624,7 @@
         <v>78</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -16608,13 +16641,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16637,16 +16670,16 @@
         <v>78</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -16696,7 +16729,7 @@
         <v>78</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4547" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4547" uniqueCount="638">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T07:59:27+00:00</t>
+    <t>2026-06-18T08:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,7 @@
   <si>
     <t>Onkologischer Versorgungsplan auf Basis von `CarePlan`.
 Das Profil ist architektonisch an den **HL7 FHIR US Multiple Chronic Conditions (MCC) eCare Plan**
-([MCCCarePlan](https://build.fhir.org/ig/HL7/fhir-us-mcc/StructureDefinition-MCCCarePlan.html))
+([MCCCarePlan](https://build.fhir.org/ig/HL7/fhir-us-mcc/StructureDefinition-mccCarePlan.html))
 angelehnt: Der CarePlan ist das zentrale, konsensbasierte Steuerobjekt, das adressierte
 Erkrankungen (`addresses`), übergeordnete Ziele (`goal`) sowie geplante und durchgeführte
 Maßnahmen (`activity`) verschiedener Versorgungsteams zusammenführt.
@@ -619,9 +619,6 @@
   </si>
   <si>
     <t>Proposals/recommendations, plans and orders all use the same structure and can exist in the same fulfillment chain.</t>
-  </si>
-  <si>
-    <t>plan</t>
   </si>
   <si>
     <t>Codes indicating the degree of authority/intentionality associated with a care plan.</t>
@@ -2352,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24">
@@ -2360,7 +2357,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="25">
@@ -2376,7 +2373,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27">
@@ -2384,7 +2381,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28">
@@ -2438,7 +2435,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35">
@@ -2474,7 +2471,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40">
@@ -2482,7 +2479,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41">
@@ -2514,7 +2511,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45">
@@ -2522,7 +2519,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46">
@@ -2538,7 +2535,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="48">
@@ -2628,7 +2625,7 @@
         <v>29</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="60">
@@ -2644,7 +2641,7 @@
         <v>33</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="62">
@@ -2665,26 +2662,26 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="67">
@@ -2700,7 +2697,7 @@
         <v>2</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="69">
@@ -2708,7 +2705,7 @@
         <v>4</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="70">
@@ -2724,7 +2721,7 @@
         <v>8</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="72">
@@ -2732,7 +2729,7 @@
         <v>10</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="73">
@@ -2786,7 +2783,7 @@
         <v>23</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="80">
@@ -2822,7 +2819,7 @@
         <v>31</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="85">
@@ -2830,7 +2827,7 @@
         <v>33</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="86">
@@ -4814,7 +4811,7 @@
         <v>84</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>85</v>
@@ -4842,7 +4839,7 @@
       </c>
       <c r="R19" s="2"/>
       <c r="S19" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>78</v>
@@ -4863,10 +4860,10 @@
         <v>182</v>
       </c>
       <c r="Z19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AA19" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AB19" t="s" s="2">
         <v>78</v>
@@ -4904,10 +4901,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -4930,19 +4927,19 @@
         <v>85</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O20" t="s" s="2">
+      <c r="P20" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="Q20" t="s" s="2">
         <v>78</v>
@@ -4967,14 +4964,14 @@
         <v>78</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AA20" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA20" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AB20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4991,7 +4988,7 @@
         <v>78</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>76</v>
@@ -5011,10 +5008,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -5037,13 +5034,13 @@
         <v>85</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -5094,7 +5091,7 @@
         <v>78</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>76</v>
@@ -5114,10 +5111,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -5140,17 +5137,17 @@
         <v>85</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M22" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q22" t="s" s="2">
         <v>78</v>
@@ -5199,7 +5196,7 @@
         <v>78</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>76</v>
@@ -5219,14 +5216,14 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
@@ -5245,13 +5242,13 @@
         <v>85</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -5302,7 +5299,7 @@
         <v>78</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>84</v>
@@ -5322,10 +5319,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -5348,16 +5345,16 @@
         <v>85</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" t="s" s="2">
@@ -5407,7 +5404,7 @@
         <v>78</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>76</v>
@@ -5427,14 +5424,14 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
@@ -5453,19 +5450,19 @@
         <v>85</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="O25" t="s" s="2">
+      <c r="P25" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="P25" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="Q25" t="s" s="2">
         <v>78</v>
@@ -5514,7 +5511,7 @@
         <v>78</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>76</v>
@@ -5534,14 +5531,14 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" t="s" s="2">
@@ -5560,13 +5557,13 @@
         <v>85</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -5617,7 +5614,7 @@
         <v>78</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>76</v>
@@ -5637,10 +5634,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -5663,16 +5660,16 @@
         <v>85</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
@@ -5722,7 +5719,7 @@
         <v>78</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>76</v>
@@ -5742,10 +5739,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5768,16 +5765,16 @@
         <v>78</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
@@ -5827,7 +5824,7 @@
         <v>78</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
@@ -5847,10 +5844,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -5873,17 +5870,17 @@
         <v>78</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q29" t="s" s="2">
         <v>78</v>
@@ -5932,7 +5929,7 @@
         <v>78</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
@@ -5952,10 +5949,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -5978,19 +5975,19 @@
         <v>85</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="O30" t="s" s="2">
+      <c r="P30" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="P30" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="Q30" t="s" s="2">
         <v>78</v>
@@ -6039,7 +6036,7 @@
         <v>78</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>76</v>
@@ -6059,10 +6056,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -6085,19 +6082,19 @@
         <v>78</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="O31" t="s" s="2">
+      <c r="P31" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="P31" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="Q31" t="s" s="2">
         <v>78</v>
@@ -6146,7 +6143,7 @@
         <v>78</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
@@ -6166,10 +6163,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -6192,19 +6189,19 @@
         <v>78</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="O32" t="s" s="2">
+      <c r="P32" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="Q32" t="s" s="2">
         <v>78</v>
@@ -6253,7 +6250,7 @@
         <v>78</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
@@ -6273,10 +6270,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -6299,17 +6296,17 @@
         <v>78</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q33" t="s" s="2">
         <v>78</v>
@@ -6358,7 +6355,7 @@
         <v>78</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>76</v>
@@ -6370,7 +6367,7 @@
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34">
@@ -6378,10 +6375,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -6404,13 +6401,13 @@
         <v>78</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -6461,7 +6458,7 @@
         <v>78</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>76</v>
@@ -6481,10 +6478,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -6510,10 +6507,10 @@
         <v>127</v>
       </c>
       <c r="M35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>144</v>
@@ -6566,7 +6563,7 @@
         <v>78</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>76</v>
@@ -6586,14 +6583,14 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
@@ -6615,10 +6612,10 @@
         <v>127</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>144</v>
@@ -6673,7 +6670,7 @@
         <v>78</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>76</v>
@@ -6693,10 +6690,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6719,16 +6716,16 @@
         <v>78</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" t="s" s="2">
@@ -6754,14 +6751,14 @@
         <v>78</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AA37" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="AB37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6778,7 +6775,7 @@
         <v>78</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>76</v>
@@ -6798,10 +6795,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6824,19 +6821,19 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="O38" t="s" s="2">
+      <c r="P38" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="Q38" t="s" s="2">
         <v>78</v>
@@ -6885,7 +6882,7 @@
         <v>78</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
@@ -6905,10 +6902,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6931,19 +6928,19 @@
         <v>78</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="O39" t="s" s="2">
+      <c r="P39" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="P39" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="Q39" t="s" s="2">
         <v>78</v>
@@ -6992,7 +6989,7 @@
         <v>78</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
@@ -7012,10 +7009,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -7038,19 +7035,19 @@
         <v>78</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="O40" t="s" s="2">
+      <c r="P40" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="Q40" t="s" s="2">
         <v>78</v>
@@ -7099,7 +7096,7 @@
         <v>78</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>76</v>
@@ -7108,7 +7105,7 @@
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>96</v>
@@ -7119,10 +7116,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -7145,17 +7142,17 @@
         <v>78</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q41" t="s" s="2">
         <v>78</v>
@@ -7204,7 +7201,7 @@
         <v>78</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
@@ -7213,7 +7210,7 @@
         <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>96</v>
@@ -7224,10 +7221,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -7250,13 +7247,13 @@
         <v>78</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -7307,7 +7304,7 @@
         <v>78</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -7327,10 +7324,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -7356,10 +7353,10 @@
         <v>127</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>144</v>
@@ -7412,7 +7409,7 @@
         <v>78</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
@@ -7432,14 +7429,14 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -7461,10 +7458,10 @@
         <v>127</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>144</v>
@@ -7519,7 +7516,7 @@
         <v>78</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
@@ -7539,10 +7536,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7568,14 +7565,14 @@
         <v>104</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>78</v>
@@ -7603,11 +7600,11 @@
         <v>182</v>
       </c>
       <c r="Z45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AA45" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AA45" t="s" s="2">
-        <v>319</v>
-      </c>
       <c r="AB45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7624,7 +7621,7 @@
         <v>78</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -7644,10 +7641,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7670,17 +7667,17 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>155</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>78</v>
@@ -7729,7 +7726,7 @@
         <v>78</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -7749,10 +7746,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7781,13 +7778,13 @@
         <v>158</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>160</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>78</v>
@@ -7836,7 +7833,7 @@
         <v>78</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -7856,10 +7853,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7882,19 +7879,19 @@
         <v>78</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="O48" t="s" s="2">
+      <c r="P48" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="Q48" t="s" s="2">
         <v>78</v>
@@ -7919,14 +7916,14 @@
         <v>78</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z48" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AA48" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AA48" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="AB48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7943,7 +7940,7 @@
         <v>78</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -7963,10 +7960,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7989,16 +7986,16 @@
         <v>78</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
@@ -8024,14 +8021,14 @@
         <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z49" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AA49" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AA49" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="AB49" t="s" s="2">
         <v>78</v>
       </c>
@@ -8048,7 +8045,7 @@
         <v>78</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -8068,10 +8065,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -8094,16 +8091,16 @@
         <v>78</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
@@ -8153,7 +8150,7 @@
         <v>78</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
@@ -8173,10 +8170,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -8199,17 +8196,17 @@
         <v>78</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q51" t="s" s="2">
         <v>78</v>
@@ -8258,7 +8255,7 @@
         <v>78</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -8278,10 +8275,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -8307,16 +8304,16 @@
         <v>104</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="O52" t="s" s="2">
+      <c r="P52" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="Q52" t="s" s="2">
         <v>78</v>
@@ -8344,11 +8341,11 @@
         <v>182</v>
       </c>
       <c r="Z52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AA52" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AA52" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AB52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8365,7 +8362,7 @@
         <v>78</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>84</v>
@@ -8385,10 +8382,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8411,16 +8408,16 @@
         <v>78</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
@@ -8470,7 +8467,7 @@
         <v>78</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
@@ -8490,10 +8487,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8516,26 +8513,26 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="O54" t="s" s="2">
+      <c r="P54" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="P54" t="s" s="2">
+      <c r="Q54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R54" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Q54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R54" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="S54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8579,7 +8576,7 @@
         <v>78</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
@@ -8599,10 +8596,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8625,17 +8622,17 @@
         <v>78</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>78</v>
@@ -8684,7 +8681,7 @@
         <v>78</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -8704,10 +8701,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8730,19 +8727,19 @@
         <v>78</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="O56" t="s" s="2">
+      <c r="P56" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>78</v>
@@ -8791,7 +8788,7 @@
         <v>78</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
@@ -8811,10 +8808,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8837,19 +8834,19 @@
         <v>78</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="O57" t="s" s="2">
-        <v>382</v>
-      </c>
       <c r="P57" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>78</v>
@@ -8898,7 +8895,7 @@
         <v>78</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
@@ -8918,10 +8915,10 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8944,13 +8941,13 @@
         <v>78</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -8977,14 +8974,14 @@
         <v>78</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z58" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA58" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AA58" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AB58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9001,7 +8998,7 @@
         <v>78</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
@@ -9021,14 +9018,14 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
@@ -9047,17 +9044,17 @@
         <v>78</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q59" t="s" s="2">
         <v>78</v>
@@ -9106,7 +9103,7 @@
         <v>78</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>76</v>
@@ -9126,10 +9123,10 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -9152,13 +9149,13 @@
         <v>78</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -9209,7 +9206,7 @@
         <v>78</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>76</v>
@@ -9229,10 +9226,10 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -9255,13 +9252,13 @@
         <v>78</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
@@ -9312,7 +9309,7 @@
         <v>78</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>76</v>
@@ -9332,10 +9329,10 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9358,17 +9355,17 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q62" t="s" s="2">
         <v>78</v>
@@ -9417,7 +9414,7 @@
         <v>78</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
@@ -9434,13 +9431,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -9466,13 +9463,13 @@
         <v>79</v>
       </c>
       <c r="M63" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="O63" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -9522,7 +9519,7 @@
         <v>78</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
@@ -9539,13 +9536,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9644,13 +9641,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9747,13 +9744,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9852,13 +9849,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9957,13 +9954,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -10062,13 +10059,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -10167,13 +10164,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10268,13 +10265,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>135</v>
@@ -10373,13 +10370,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10480,13 +10477,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10512,16 +10509,16 @@
         <v>148</v>
       </c>
       <c r="M73" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>151</v>
       </c>
       <c r="P73" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q73" t="s" s="2">
         <v>78</v>
@@ -10570,7 +10567,7 @@
         <v>78</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>76</v>
@@ -10587,13 +10584,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10619,16 +10616,16 @@
         <v>104</v>
       </c>
       <c r="M74" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="O74" t="s" s="2">
+      <c r="P74" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>78</v>
@@ -10656,11 +10653,11 @@
         <v>182</v>
       </c>
       <c r="Z74" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AA74" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AA74" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="AB74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10677,7 +10674,7 @@
         <v>78</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>84</v>
@@ -10694,13 +10691,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10723,13 +10720,13 @@
         <v>85</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
@@ -10759,11 +10756,11 @@
         <v>108</v>
       </c>
       <c r="Z75" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AA75" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AA75" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="AB75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10780,7 +10777,7 @@
         <v>78</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -10797,13 +10794,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10826,17 +10823,17 @@
         <v>85</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>78</v>
@@ -10861,11 +10858,11 @@
         <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Z76" s="2"/>
       <c r="AA76" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AB76" t="s" s="2">
         <v>78</v>
@@ -10883,7 +10880,7 @@
         <v>78</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>76</v>
@@ -10900,13 +10897,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10929,19 +10926,19 @@
         <v>85</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="O77" t="s" s="2">
+      <c r="P77" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>78</v>
@@ -10969,11 +10966,11 @@
         <v>108</v>
       </c>
       <c r="Z77" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AA77" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AA77" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="AB77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10990,7 +10987,7 @@
         <v>78</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -11007,13 +11004,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11036,19 +11033,19 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M78" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="O78" t="s" s="2">
+      <c r="P78" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="Q78" t="s" s="2">
         <v>78</v>
@@ -11073,13 +11070,13 @@
         <v>78</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AA78" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AB78" t="s" s="2">
         <v>78</v>
@@ -11097,7 +11094,7 @@
         <v>78</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>84</v>
@@ -11114,13 +11111,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11143,17 +11140,17 @@
         <v>85</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q79" t="s" s="2">
         <v>78</v>
@@ -11202,7 +11199,7 @@
         <v>78</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>84</v>
@@ -11219,13 +11216,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11248,17 +11245,17 @@
         <v>85</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q80" t="s" s="2">
         <v>78</v>
@@ -11283,14 +11280,14 @@
         <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z80" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA80" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AA80" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="AB80" t="s" s="2">
         <v>78</v>
       </c>
@@ -11307,7 +11304,7 @@
         <v>78</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -11324,13 +11321,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11353,19 +11350,19 @@
         <v>78</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="O81" t="s" s="2">
+      <c r="P81" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>78</v>
@@ -11414,7 +11411,7 @@
         <v>78</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -11423,21 +11420,21 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AK81" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11460,13 +11457,13 @@
         <v>78</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -11517,7 +11514,7 @@
         <v>78</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>76</v>
@@ -11534,13 +11531,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11566,10 +11563,10 @@
         <v>127</v>
       </c>
       <c r="M83" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>144</v>
@@ -11622,7 +11619,7 @@
         <v>78</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>76</v>
@@ -11639,17 +11636,17 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" t="s" s="2">
@@ -11671,10 +11668,10 @@
         <v>127</v>
       </c>
       <c r="M84" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>144</v>
@@ -11729,7 +11726,7 @@
         <v>78</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>76</v>
@@ -11746,13 +11743,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11775,13 +11772,13 @@
         <v>85</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -11808,14 +11805,14 @@
         <v>78</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z85" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AA85" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AA85" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="AB85" t="s" s="2">
         <v>78</v>
       </c>
@@ -11832,7 +11829,7 @@
         <v>78</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -11841,7 +11838,7 @@
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>96</v>
@@ -11849,13 +11846,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11878,16 +11875,16 @@
         <v>85</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
@@ -11913,10 +11910,10 @@
         <v>78</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -11937,7 +11934,7 @@
         <v>78</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -11946,7 +11943,7 @@
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>96</v>
@@ -11954,13 +11951,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11983,17 +11980,17 @@
         <v>85</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>78</v>
@@ -12042,7 +12039,7 @@
         <v>78</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
@@ -12059,13 +12056,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12088,16 +12085,16 @@
         <v>85</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
@@ -12147,7 +12144,7 @@
         <v>78</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>76</v>
@@ -12164,13 +12161,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -12193,16 +12190,16 @@
         <v>78</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N89" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O89" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -12252,7 +12249,7 @@
         <v>78</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -12269,13 +12266,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -12298,16 +12295,16 @@
         <v>85</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
@@ -12357,7 +12354,7 @@
         <v>78</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>76</v>
@@ -12374,13 +12371,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12403,17 +12400,17 @@
         <v>78</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q91" t="s" s="2">
         <v>78</v>
@@ -12462,7 +12459,7 @@
         <v>78</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>76</v>
@@ -12479,13 +12476,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -12508,19 +12505,19 @@
         <v>78</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M92" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="O92" t="s" s="2">
+      <c r="P92" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="Q92" t="s" s="2">
         <v>78</v>
@@ -12569,7 +12566,7 @@
         <v>78</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -12586,13 +12583,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12615,19 +12612,19 @@
         <v>78</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="O93" t="s" s="2">
+      <c r="P93" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="Q93" t="s" s="2">
         <v>78</v>
@@ -12652,13 +12649,13 @@
         <v>78</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>78</v>
@@ -12676,7 +12673,7 @@
         <v>78</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -12693,13 +12690,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12722,19 +12719,19 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="O94" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="P94" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>78</v>
@@ -12783,7 +12780,7 @@
         <v>78</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
@@ -12800,7 +12797,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>128</v>
@@ -12903,13 +12900,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12932,13 +12929,13 @@
         <v>78</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M96" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
@@ -12989,7 +12986,7 @@
         <v>78</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>76</v>
@@ -13006,13 +13003,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13083,7 +13080,7 @@
         <v>130</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AE97" t="s" s="2">
         <v>78</v>
@@ -13092,7 +13089,7 @@
         <v>131</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
@@ -13109,13 +13106,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13141,13 +13138,13 @@
         <v>98</v>
       </c>
       <c r="M98" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
@@ -13155,7 +13152,7 @@
       </c>
       <c r="R98" s="2"/>
       <c r="S98" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>78</v>
@@ -13197,7 +13194,7 @@
         <v>78</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>84</v>
@@ -13214,13 +13211,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13243,13 +13240,13 @@
         <v>78</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M99" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -13280,7 +13277,7 @@
       </c>
       <c r="Z99" s="2"/>
       <c r="AA99" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AB99" t="s" s="2">
         <v>78</v>
@@ -13298,7 +13295,7 @@
         <v>78</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
@@ -13315,17 +13312,17 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s" s="2">
@@ -13347,10 +13344,10 @@
         <v>79</v>
       </c>
       <c r="M100" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -13401,7 +13398,7 @@
         <v>78</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -13418,13 +13415,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13523,13 +13520,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13626,13 +13623,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13731,13 +13728,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13836,13 +13833,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13941,13 +13938,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14046,13 +14043,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14147,13 +14144,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>135</v>
@@ -14252,13 +14249,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14359,13 +14356,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14391,10 +14388,10 @@
         <v>148</v>
       </c>
       <c r="M110" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
@@ -14445,7 +14442,7 @@
         <v>78</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
@@ -14462,13 +14459,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14494,13 +14491,13 @@
         <v>104</v>
       </c>
       <c r="M111" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
@@ -14529,11 +14526,11 @@
         <v>182</v>
       </c>
       <c r="Z111" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AA111" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AA111" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="AB111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14550,7 +14547,7 @@
         <v>78</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>84</v>
@@ -14567,13 +14564,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14596,13 +14593,13 @@
         <v>78</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M112" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
@@ -14653,7 +14650,7 @@
         <v>78</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -14670,13 +14667,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14699,13 +14696,13 @@
         <v>78</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M113" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -14756,7 +14753,7 @@
         <v>78</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>76</v>
@@ -14773,13 +14770,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -14805,10 +14802,10 @@
         <v>127</v>
       </c>
       <c r="M114" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>144</v>
@@ -14861,7 +14858,7 @@
         <v>78</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>76</v>
@@ -14878,17 +14875,17 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" t="s" s="2">
@@ -14910,10 +14907,10 @@
         <v>127</v>
       </c>
       <c r="M115" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N115" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O115" t="s" s="2">
         <v>144</v>
@@ -14968,7 +14965,7 @@
         <v>78</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>76</v>
@@ -14985,13 +14982,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -15017,10 +15014,10 @@
         <v>104</v>
       </c>
       <c r="M116" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -15050,11 +15047,11 @@
         <v>182</v>
       </c>
       <c r="Z116" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AA116" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AA116" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="AB116" t="s" s="2">
         <v>78</v>
       </c>
@@ -15071,7 +15068,7 @@
         <v>78</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>84</v>
@@ -15088,13 +15085,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -15117,13 +15114,13 @@
         <v>78</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M117" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -15174,7 +15171,7 @@
         <v>78</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>84</v>
@@ -15191,13 +15188,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -15220,16 +15217,16 @@
         <v>85</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M118" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N118" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
@@ -15255,14 +15252,14 @@
         <v>78</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z118" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AA118" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AA118" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="AB118" t="s" s="2">
         <v>78</v>
       </c>
@@ -15279,7 +15276,7 @@
         <v>78</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>76</v>
@@ -15296,13 +15293,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -15325,13 +15322,13 @@
         <v>85</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M119" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N119" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
@@ -15382,7 +15379,7 @@
         <v>78</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -15399,13 +15396,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -15428,13 +15425,13 @@
         <v>78</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M120" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
@@ -15485,7 +15482,7 @@
         <v>78</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>76</v>
@@ -15502,13 +15499,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -15534,10 +15531,10 @@
         <v>127</v>
       </c>
       <c r="M121" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O121" t="s" s="2">
         <v>144</v>
@@ -15590,7 +15587,7 @@
         <v>78</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>76</v>
@@ -15607,17 +15604,17 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" t="s" s="2">
@@ -15639,10 +15636,10 @@
         <v>127</v>
       </c>
       <c r="M122" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>144</v>
@@ -15697,7 +15694,7 @@
         <v>78</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>76</v>
@@ -15714,13 +15711,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15743,13 +15740,13 @@
         <v>85</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M123" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -15800,7 +15797,7 @@
         <v>78</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>84</v>
@@ -15817,13 +15814,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -15846,13 +15843,13 @@
         <v>85</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M124" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N124" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -15882,11 +15879,11 @@
         <v>108</v>
       </c>
       <c r="Z124" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AA124" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="AA124" t="s" s="2">
-        <v>606</v>
-      </c>
       <c r="AB124" t="s" s="2">
         <v>78</v>
       </c>
@@ -15903,7 +15900,7 @@
         <v>78</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -15920,13 +15917,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -15949,13 +15946,13 @@
         <v>85</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -16006,7 +16003,7 @@
         <v>78</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>76</v>
@@ -16023,13 +16020,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16052,13 +16049,13 @@
         <v>85</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -16109,7 +16106,7 @@
         <v>78</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>84</v>
@@ -16126,13 +16123,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -16155,13 +16152,13 @@
         <v>85</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -16212,7 +16209,7 @@
         <v>78</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>76</v>
@@ -16229,13 +16226,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -16258,13 +16255,13 @@
         <v>85</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N128" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
@@ -16315,7 +16312,7 @@
         <v>78</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>76</v>
@@ -16332,13 +16329,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -16361,13 +16358,13 @@
         <v>78</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
@@ -16418,7 +16415,7 @@
         <v>78</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>76</v>
@@ -16435,13 +16432,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16464,13 +16461,13 @@
         <v>78</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
@@ -16521,7 +16518,7 @@
         <v>78</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>76</v>
@@ -16538,17 +16535,17 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" t="s" s="2">
@@ -16567,13 +16564,13 @@
         <v>78</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M131" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -16624,7 +16621,7 @@
         <v>78</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -16641,13 +16638,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16670,16 +16667,16 @@
         <v>78</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -16729,7 +16726,7 @@
         <v>78</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:58+00:00</t>
+    <t>2026-06-18T08:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10287,7 +10287,7 @@
         <v>84</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>78</v>
@@ -10814,7 +10814,7 @@
         <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>78</v>
@@ -12496,7 +12496,7 @@
         <v>77</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>78</v>
@@ -12603,7 +12603,7 @@
         <v>77</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>78</v>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:27+00:00</t>
+    <t>2026-06-18T08:56:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3862,7 +3862,7 @@
         <v>84</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
@@ -5441,7 +5441,7 @@
         <v>84</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>78</v>
@@ -5651,7 +5651,7 @@
         <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>78</v>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:56:30+00:00</t>
+    <t>2026-06-18T10:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:39:29+00:00</t>
+    <t>2026-06-18T11:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:45:59+00:00</t>
+    <t>2026-06-24T07:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:12:52+00:00</t>
+    <t>2026-07-10T09:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/all-profiles.xlsx
+++ b/ci-build/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
